--- a/🧭 Atlas de l'IA.xlsx
+++ b/🧭 Atlas de l'IA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://atos365-my.sharepoint.com/personal/brice_dardeau_atos_net/Documents/Documents/GitHub/Playbook-IA-Francophone-de-Brice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="535" documentId="8_{B857BCC3-7EE5-4379-869F-79AC47428AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{161FDE2B-0FD4-48E4-9531-E87B7A7B08F8}"/>
+  <xr:revisionPtr revIDLastSave="818" documentId="8_{B857BCC3-7EE5-4379-869F-79AC47428AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C32A5F9F-E246-4798-A7DA-276939BE39A6}"/>
   <bookViews>
     <workbookView xWindow="-25320" yWindow="3285" windowWidth="25440" windowHeight="15270" activeTab="3" xr2:uid="{02F492F3-3D1D-4FEA-ACD4-D822B597EB0E}"/>
   </bookViews>
@@ -16,8 +16,9 @@
     <sheet name="Glossaire" sheetId="1" r:id="rId1"/>
     <sheet name="Agents" sheetId="3" r:id="rId2"/>
     <sheet name="Solutions &amp; Usages" sheetId="5" r:id="rId3"/>
-    <sheet name="Ressources" sheetId="6" r:id="rId4"/>
-    <sheet name="PrPPT" sheetId="2" r:id="rId5"/>
+    <sheet name="Certifications" sheetId="7" r:id="rId4"/>
+    <sheet name="Prompts" sheetId="6" r:id="rId5"/>
+    <sheet name="PrPPT" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="683">
   <si>
     <t>Terme</t>
   </si>
@@ -60,12 +61,6 @@
 audio
 vidéo
 LLM</t>
-  </si>
-  <si>
-    <t>Large Language Model</t>
-  </si>
-  <si>
-    <t>GPT Claude Gemini</t>
   </si>
   <si>
     <t>Prompt</t>
@@ -245,13 +240,6 @@
   </si>
   <si>
     <t>Framework d'orchestration multi-agents. Atos le présente comme une extension permettant de créer des applications multi-acteurs et des runtimes agentiques sophistiqués.</t>
-  </si>
-  <si>
-    <t>Pour réaliser un bon prommpt, vous avez besoin, d'un contexte, d'un objectif, d'identifier la source et de définir les attentes.
-Fournir un contexte : pourquoi en avez-vous besoin et qui est impliqué ? Décrivez la situation, que vous soyez en train de préparer une réunion cliente, d’analyser un rapport trimestriel ou de créer une présentation de la direction. Contrairement à la recherche traditionnelle, Copilot répond le mieux aux invites détaillées et descriptives.
-Décrire un objectif : Que voulez-vous que Copilot fasse ? Spécifiez la sortie : un résumé, un premier brouillon, une liste d’éléments d’action, une visualisation de données. Si vous avez un format à l’esprit, décrivez-le.
-Définir une source : Où doit se trouver Copilot ? Référencez des fichiers, des e-mails, des réunions ou des notes de réunion spécifiques afin que Copilot extrait le contenu approprié. Avec votre licence Microsoft 365 Copilot, vous pouvez référencer vos données professionnelles (e-mails, réunions et fichiers) directement dans vos invites.
-Définir les attentes : Comment Copilot doit-il répondre ? Spécifiez l’audience, le ton, la longueur ou la structure. Une réponse pour la haute direction se lit différemment d’une réponse pour une mise à jour de l’équipe de projet.</t>
   </si>
   <si>
     <t>Work IQ</t>
@@ -1583,9 +1571,6 @@
     <t>Agent IA d'OpenAI capable de naviguer sur le web, cliquer, remplir des formulaires et exécuter des tâches dans un navigateur. Représente l'évolution vers des agents autonomes capables d'agir dans le monde numérique.</t>
   </si>
   <si>
-    <t>Cowork / Claude for Work</t>
-  </si>
-  <si>
     <t>Offre entreprise d'Anthropic intégrant Claude dans les outils de travail. Équivalent de M365 Copilot côté Anthropic. Permet à l'IA d'accéder aux documents et données de l'organisation.</t>
   </si>
   <si>
@@ -1698,13 +1683,669 @@
   </si>
   <si>
     <t>https://platform.openai.com/docs/guides/prompt-engineering</t>
+  </si>
+  <si>
+    <t>Pour réaliser un bon prompt, vous avez besoin, d'un contexte, d'un objectif, d'identifier la source et de définir les attentes.
+Fournir un contexte : pourquoi en avez-vous besoin et qui est impliqué ? Décrivez la situation, que vous soyez en train de préparer une réunion cliente, d’analyser un rapport trimestriel ou de créer une présentation de la direction. Contrairement à la recherche traditionnelle, Copilot répond le mieux aux invites détaillées et descriptives.
+Décrire un objectif : Que voulez-vous que Copilot fasse ? Spécifiez la sortie : un résumé, un premier brouillon, une liste d’éléments d’action, une visualisation de données. Si vous avez un format à l’esprit, décrivez-le.
+Définir une source : Où doit se trouver Copilot ? Référencez des fichiers, des e-mails, des réunions ou des notes de réunion spécifiques afin que Copilot extrait le contenu approprié. Avec votre licence Microsoft 365 Copilot, vous pouvez référencer vos données professionnelles (e-mails, réunions et fichiers) directement dans vos invites.
+Définir les attentes : Comment Copilot doit-il répondre ? Spécifiez l’audience, le ton, la longueur ou la structure. Une réponse pour la haute direction se lit différemment d’une réponse pour une mise à jour de l’équipe de projet.</t>
+  </si>
+  <si>
+    <t>Sécurité</t>
+  </si>
+  <si>
+    <t>Architecture</t>
+  </si>
+  <si>
+    <t>Prompting</t>
+  </si>
+  <si>
+    <t>Données</t>
+  </si>
+  <si>
+    <t>Modèle</t>
+  </si>
+  <si>
+    <t>Généralité</t>
+  </si>
+  <si>
+    <t>Large Language Model (Grand modèle de langage). Modèle d'IA entraîné sur de vastes corpus de textes pour comprendre et générer du langage naturel.
+Exemples :
+• OpenAI : GPT-4, GPT-4o, o1, o3
+• Anthropic : Claude 3.5 Sonnet, Claude 3 Opus
+• Google : Gemini Pro, Gemini Ultra
+• Meta : Llama 3, Llama 3.1
+• Mistral AI : Mistral Large, Mixtral
+• Microsoft : Phi-3, Phi-4</t>
+  </si>
+  <si>
+    <t>Modèles de langage plus petits et optimisés pour des tâches spécifiques ou des environnements contraints.
+Exemples :
+• Microsoft Phi-3/Phi-4
+• Google Gemma
+• Meta Llama 3.2 (versions légères)
+Avantages : rapidité, coût réduit, déploiement local possible.</t>
+  </si>
+  <si>
+    <t>Modèle capable de traiter plusieurs types de données : texte, image, audio, vidéo.
+Exemples :
+• GPT-4o (texte + image + audio)
+• Gemini (texte + image + vidéo)
+• Claude 3 (texte + image)
+Permet des interactions plus riches et naturelles.</t>
+  </si>
+  <si>
+    <t>Modèles optimisés pour le raisonnement complexe et la résolution de problèmes.
+Exemples :
+• OpenAI o1, o3
+• Google Gemini 2.0 Flash Thinking
+Utilisent des techniques de "thinking" avant de répondre.</t>
+  </si>
+  <si>
+    <t>Pattern</t>
+  </si>
+  <si>
+    <t>Type de modèle IA</t>
+  </si>
+  <si>
+    <t>Agentique</t>
+  </si>
+  <si>
+    <t>Large Language Model (LLM) – 3e/4e génération</t>
+  </si>
+  <si>
+    <t>SLM (Small Language Model) – 4e génération</t>
+  </si>
+  <si>
+    <t>Modèle multimodal – 4e génération</t>
+  </si>
+  <si>
+    <t>Modèle de raisonnement – 5e génération</t>
+  </si>
+  <si>
+    <t>Générations d'IA</t>
+  </si>
+  <si>
+    <t>Évolution historique des modèles d'intelligence artificielle :
+🔹 1re génération – IA symbolique (années 1950-1980)
+Systèmes basés sur des règles logiques et la manipulation de symboles.
+Exemples : ELIZA, systèmes experts (MYCIN, DENDRAL)
+🔹 2e génération – Machine Learning (années 1990-2010)
+Apprentissage à partir de données avec algorithmes statistiques.
+Exemples : SVM, Random Forest, réseaux de neurones classiques, IBM Watson (Jeopardy)
+🔹 3e génération – Deep Learning (années 2012-2020)
+Réseaux de neurones profonds, architectures Transformer (2017).
+Exemples : BERT, GPT-2, GPT-3, AlphaGo, reconnaissance d'images (ResNet)
+🔹 4e génération – IA Générative (2022-2024)
+Modèles de langage massifs, multimodaux, assistants conversationnels.
+Exemples : GPT-4, Claude 3, Gemini, DALL-E 3, Midjourney, Copilot, Phi-3/4 (SLM)
+🔹 5e génération – IA Agentique &amp; Raisonnement (2024-2025)
+Modèles capables de raisonner, planifier et agir de manière autonome.
+Exemples : OpenAI o1/o3, Gemini 2.0 Flash Thinking, agents Copilot Studio, Operator (OpenAI)
+🔹 6e génération – AGI / IA Générale (à venir)
+Intelligence artificielle capable d'égaler ou surpasser l'intelligence humaine sur toutes les tâches cognitives. Autonomie complète, apprentissage continu, transfert de connaissances entre domaines.
+Exemples attendus : GPT-5 (?), Project Stargate, initiatives DeepMind, recherches Anthropic sur l'alignement</t>
+  </si>
+  <si>
+    <t>Copilot Pages</t>
+  </si>
+  <si>
+    <t>Canvas collaboratif alimenté par l'IA dans Microsoft 365. Permet de créer des pages partagées où les utilisateurs peuvent travailler ensemble avec l'assistance de Copilot pour synthétiser, organiser et enrichir le contenu.</t>
+  </si>
+  <si>
+    <t>Copilot Actions</t>
+  </si>
+  <si>
+    <t>Automatisations créées et déclenchées par Copilot pour exécuter des tâches répétitives. Permettent de transformer des instructions en langage naturel en workflows automatisés.</t>
+  </si>
+  <si>
+    <t>SharePoint Premium</t>
+  </si>
+  <si>
+    <t>Ensemble de fonctionnalités IA avancées pour SharePoint (anciennement Syntex). Inclut le traitement intelligent des documents, la classification automatique et l'extraction de métadonnées par IA.</t>
+  </si>
+  <si>
+    <t>Loop</t>
+  </si>
+  <si>
+    <t>Application Microsoft de collaboration en temps réel. Les composants Loop sont des blocs de contenu portables et synchronisés entre les apps M365, avec Copilot intégré pour la co-création.</t>
+  </si>
+  <si>
+    <t>Copilot Lab</t>
+  </si>
+  <si>
+    <t>Espace d'apprentissage et d'expérimentation pour maîtriser Copilot. Propose des prompts recommandés, des conseils et permet de sauvegarder ses prompts favoris.</t>
+  </si>
+  <si>
+    <t>Microsoft Places</t>
+  </si>
+  <si>
+    <t>Application M365 pour optimiser le travail hybride. Utilise l'IA pour coordonner la présence au bureau, les réservations d'espaces et la collaboration en présentiel.</t>
+  </si>
+  <si>
+    <t>AutoGPT</t>
+  </si>
+  <si>
+    <t>Agent IA autonome open source capable de décomposer un objectif en sous-tâches, les exécuter et itérer jusqu'à l'accomplissement. Pionnier du mouvement agentique (2023).</t>
+  </si>
+  <si>
+    <t>CrewAI</t>
+  </si>
+  <si>
+    <t>Framework Python pour créer des équipes d'agents IA collaboratifs. Chaque agent a un rôle, des compétences et peut déléguer des tâches à d'autres agents.</t>
+  </si>
+  <si>
+    <t>Function Calling</t>
+  </si>
+  <si>
+    <t>Capacité d'un LLM à générer des appels de fonction structurés (JSON) plutôt que du texte. Permet au modèle d'interagir avec des APIs et outils externes de manière fiable.</t>
+  </si>
+  <si>
+    <t>Planning (IA)</t>
+  </si>
+  <si>
+    <t>Capacité d'un agent IA à décomposer un objectif complexe en étapes, établir un plan d'action et l'adapter en fonction des résultats. Composant clé de l'IA agentique.</t>
+  </si>
+  <si>
+    <t>Memory (agents)</t>
+  </si>
+  <si>
+    <t>Système permettant aux agents de conserver des informations entre les interactions.
+• Mémoire court terme : contexte de la conversation
+• Mémoire long terme : faits persistants
+• Mémoire épisodique : expériences passées</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>Application Programming Interface. Interface permettant à des applications de communiquer entre elles. Les LLM sont généralement accessibles via des APIs REST (OpenAI API, Azure OpenAI, etc.).</t>
+  </si>
+  <si>
+    <t>Tokenization</t>
+  </si>
+  <si>
+    <t>Processus de découpage d'un texte en tokens (unités de base) pour le traitement par un LLM. Différents tokenizers existent (BPE, WordPiece, SentencePiece). Un mot peut correspondre à 1 ou plusieurs tokens.</t>
+  </si>
+  <si>
+    <t>Perplexity (métrique)</t>
+  </si>
+  <si>
+    <t>Métrique mesurant la qualité d'un modèle de langage. Plus la perplexité est basse, meilleur est le modèle. Indique à quel point le modèle est "surpris" par le texte qu'il prédit.</t>
+  </si>
+  <si>
+    <t>Benchmark (IA)</t>
+  </si>
+  <si>
+    <t>Ensemble de tests standardisés pour évaluer les performances des modèles IA.
+Exemples :
+• MMLU : connaissances générales
+• HumanEval : code
+• GSM8K : mathématiques
+• HellaSwag : raisonnement</t>
+  </si>
+  <si>
+    <t>Quantization</t>
+  </si>
+  <si>
+    <t>Technique de compression des modèles IA en réduisant la précision des poids (ex: float32 → int8). Permet de déployer des modèles sur des appareils à ressources limitées avec une perte de qualité minimale.</t>
+  </si>
+  <si>
+    <t>LoRA / QLoRA</t>
+  </si>
+  <si>
+    <t>Low-Rank Adaptation. Technique de fine-tuning efficace qui n'entraîne qu'une petite partie des paramètres du modèle. QLoRA combine LoRA avec la quantization pour réduire encore les ressources nécessaires.</t>
+  </si>
+  <si>
+    <t>Prompt Engineering</t>
+  </si>
+  <si>
+    <t>Discipline consistant à concevoir et optimiser les prompts pour obtenir les meilleures réponses des LLM. Inclut la structuration, le contexte, les exemples et les contraintes.</t>
+  </si>
+  <si>
+    <t>Self-Consistency</t>
+  </si>
+  <si>
+    <t>Technique de prompting où l'on génère plusieurs réponses avec raisonnement, puis on sélectionne la réponse la plus fréquente. Améliore la fiabilité sur les problèmes de raisonnement.</t>
+  </si>
+  <si>
+    <t>Tree of Thought (ToT)</t>
+  </si>
+  <si>
+    <t>Évolution du Chain of Thought. Le modèle explore plusieurs branches de raisonnement en parallèle, évalue chaque chemin et sélectionne le plus prometteur. Utile pour les problèmes complexes.</t>
+  </si>
+  <si>
+    <t>Role Prompting</t>
+  </si>
+  <si>
+    <t>Technique consistant à assigner un rôle ou une persona au modèle ("Tu es un expert en..."). Influence le ton, le niveau de détail et l'expertise des réponses.</t>
+  </si>
+  <si>
+    <t>Jailbreak</t>
+  </si>
+  <si>
+    <t>Technique visant à contourner les guardrails et restrictions d'un modèle IA pour obtenir des réponses normalement interdites. Les fournisseurs renforcent continuellement leurs protections contre ces attaques.</t>
+  </si>
+  <si>
+    <t>Responsible AI</t>
+  </si>
+  <si>
+    <t>Cadre de principes Microsoft pour une IA éthique et responsable.
+Piliers :
+• Équité
+• Fiabilité et sécurité
+• Confidentialité
+• Inclusivité
+• Transparence
+• Responsabilité</t>
+  </si>
+  <si>
+    <t>Biais (IA)</t>
+  </si>
+  <si>
+    <t>Tendance d'un modèle IA à produire des résultats systématiquement faussés en raison de biais dans les données d'entraînement ou la conception. Peut perpétuer des stéréotypes ou discriminations.</t>
+  </si>
+  <si>
+    <t>Explainability / XAI</t>
+  </si>
+  <si>
+    <t>IA Explicable. Capacité à comprendre et expliquer comment un modèle IA arrive à ses décisions. Essentiel pour la confiance, l'audit et la conformité réglementaire (EU AI Act).</t>
+  </si>
+  <si>
+    <t>Data Loss Prevention (DLP)</t>
+  </si>
+  <si>
+    <t>Ensemble de politiques et outils pour empêcher la fuite de données sensibles. Dans le contexte Copilot, le DLP contrôle quelles informations peuvent être partagées avec l'IA.</t>
+  </si>
+  <si>
+    <t>Sensitivity Labels</t>
+  </si>
+  <si>
+    <t>Étiquettes de confidentialité Microsoft 365 (Public, Interne, Confidentiel, Très confidentiel). Copilot respecte ces étiquettes et ne peut pas accéder aux contenus au-delà des permissions de l'utilisateur.</t>
+  </si>
+  <si>
+    <t>Azure OpenAI Service</t>
+  </si>
+  <si>
+    <t>Service cloud Azure donnant accès aux modèles OpenAI (GPT-4, DALL-E, Whisper) avec la sécurité et conformité entreprise Azure. C'est le backend de Microsoft 365 Copilot.</t>
+  </si>
+  <si>
+    <t>Entreprise d'IA fondée par d'anciens membres d'OpenAI. Créateur de Claude. Focus sur la sécurité de l'IA (AI Safety) et l'alignement. Techniques notables : Constitutional AI, RLHF.</t>
+  </si>
+  <si>
+    <t>Entreprise d'IA créatrice de GPT, DALL-E, Whisper et ChatGPT. Partenaire stratégique de Microsoft. Pionnière de l'IA générative grand public et des modèles de raisonnement (o1, o3).</t>
+  </si>
+  <si>
+    <t>Plateforme communautaire pour le partage de modèles IA, datasets et applications. Hub central de l'écosystème open source ML. Propose aussi des outils (Transformers, Datasets, Spaces).</t>
+  </si>
+  <si>
+    <t>Foundation Model</t>
+  </si>
+  <si>
+    <t>Modèle IA de grande taille pré-entraîné sur des données massives, servant de base pour diverses applications. Exemples : GPT-4, Claude, Llama. Peut être adapté via fine-tuning ou prompting.</t>
+  </si>
+  <si>
+    <t>Semantic Search</t>
+  </si>
+  <si>
+    <t>Recherche basée sur le sens et l'intention plutôt que sur la correspondance exacte de mots-clés. Utilise les embeddings pour trouver des résultats conceptuellement similaires à la requête.</t>
+  </si>
+  <si>
+    <t>Similarity Search</t>
+  </si>
+  <si>
+    <t>Recherche de vecteurs (embeddings) similaires dans une base vectorielle. Utilise des métriques de distance (cosine, euclidienne) pour trouver les documents les plus proches sémantiquement.</t>
+  </si>
+  <si>
+    <t>Indexing (IA)</t>
+  </si>
+  <si>
+    <t>Processus de préparation des documents pour la recherche :
+1. Chunking (découpage)
+2. Embedding (vectorisation)
+3. Stockage dans une base vectorielle
+Étape essentielle du RAG.</t>
+  </si>
+  <si>
+    <t>Data Lakehouse</t>
+  </si>
+  <si>
+    <t>Architecture de données combinant les avantages du Data Lake (stockage brut, flexible) et du Data Warehouse (structure, performance). Exemples : Databricks, Microsoft Fabric.</t>
+  </si>
+  <si>
+    <t>Certification</t>
+  </si>
+  <si>
+    <t>Niveau</t>
+  </si>
+  <si>
+    <t>Pour qui ?</t>
+  </si>
+  <si>
+    <t>Business</t>
+  </si>
+  <si>
+    <t>Business / Management</t>
+  </si>
+  <si>
+    <t>Associate</t>
+  </si>
+  <si>
+    <t>Fundamentals</t>
+  </si>
+  <si>
+    <t>Expert</t>
+  </si>
+  <si>
+    <t>Specialty</t>
+  </si>
+  <si>
+    <t>Classement personnalisé : priorité à Microsoft 365 Copilot, puis socle IA, Power Platform et construction d’agents. Niveaux vérifiés sur Microsoft Learn le 12/08/2026.</t>
+  </si>
+  <si>
+    <t>Niveau affiché</t>
+  </si>
+  <si>
+    <t>Priorité</t>
+  </si>
+  <si>
+    <t>Débutant</t>
+  </si>
+  <si>
+    <t>Utilisateurs avancés de Copilot, BA, knowledge workers</t>
+  </si>
+  <si>
+    <t>Immédiate</t>
+  </si>
+  <si>
+    <t>Fundamentals / Technique</t>
+  </si>
+  <si>
+    <t>Débutants IA, profils métier ou techniques</t>
+  </si>
+  <si>
+    <t>Haute</t>
+  </si>
+  <si>
+    <t>Fundamentals / Low-code</t>
+  </si>
+  <si>
+    <t>BA, Citizen Developers, makers</t>
+  </si>
+  <si>
+    <t>Intermédiaire</t>
+  </si>
+  <si>
+    <t>Associate / Builder</t>
+  </si>
+  <si>
+    <t>Builders avancés, développeurs, consultants Power Platform</t>
+  </si>
+  <si>
+    <t>Moyen terme</t>
+  </si>
+  <si>
+    <t>Fundamentals / Data</t>
+  </si>
+  <si>
+    <t>BA orientés data, débutants Azure Data</t>
+  </si>
+  <si>
+    <t>Complément</t>
+  </si>
+  <si>
+    <t>Business / Leadership</t>
+  </si>
+  <si>
+    <t>Managers, sponsors IA, responsables transformation</t>
+  </si>
+  <si>
+    <t>Selon le rôle</t>
+  </si>
+  <si>
+    <t>RÉFÉRENTIEL — NIVEAUX, FAMILLES ET FILIÈRES</t>
+  </si>
+  <si>
+    <t>Repère</t>
+  </si>
+  <si>
+    <t>Nature</t>
+  </si>
+  <si>
+    <t>Exemples dans ce parcours</t>
+  </si>
+  <si>
+    <t>Niveau de difficulté indiqué sur les pages Microsoft Learn ; il ne décrit pas la séniorité du poste.</t>
+  </si>
+  <si>
+    <t>AB-730, AB-731, AI-900, PL-900, DP-900</t>
+  </si>
+  <si>
+    <t>Niveau nécessitant une pratique plus approfondie et une capacité d’intégration ou de construction.</t>
+  </si>
+  <si>
+    <t>AB-620</t>
+  </si>
+  <si>
+    <t>Famille de certification</t>
+  </si>
+  <si>
+    <t>Certification de socle, généralement identifiée par un code d’examen se terminant par -900.</t>
+  </si>
+  <si>
+    <t>AI-900, PL-900, DP-900</t>
+  </si>
+  <si>
+    <t>Certification basée sur un rôle, généralement de niveau intermédiaire et orientée mise en œuvre.</t>
+  </si>
+  <si>
+    <t>AI Agent Builder Associate (AB-620)</t>
+  </si>
+  <si>
+    <t>Certification avancée validant la maîtrise d’un rôle et de scénarios complexes.</t>
+  </si>
+  <si>
+    <t>Aucune dans la sélection actuelle</t>
+  </si>
+  <si>
+    <t>Certification spécialisée sur un domaine ou une charge de travail précise.</t>
+  </si>
+  <si>
+    <t>Filière ou public</t>
+  </si>
+  <si>
+    <t>Orientation métier ou leadership : ce n’est pas un niveau Microsoft. C’est pourquoi elle ne figurait pas dans l’ancien référentiel des niveaux.</t>
+  </si>
+  <si>
+    <t>AB-730 (Business), AB-731 (Leadership)</t>
+  </si>
+  <si>
+    <t>Applied Skills</t>
+  </si>
+  <si>
+    <t>Autre type de titre</t>
+  </si>
+  <si>
+    <t>Titre court basé sur une évaluation pratique en laboratoire ; distinct d’une certification complète.</t>
+  </si>
+  <si>
+    <t>Objectif et compétences clés</t>
+  </si>
+  <si>
+    <t>Ordre</t>
+  </si>
+  <si>
+    <t>Intérêt / moment conseillé</t>
+  </si>
+  <si>
+    <t>Améliorer les résultats métier avec l’IA générative et Microsoft 365 Copilot, sans coder.
+Compétences : Fondamentaux GenAI ; prompts et conversations ; agents ; rédaction et analyse de contenu métier</t>
+  </si>
+  <si>
+    <t>⭐⭐⭐⭐⭐ Cible la plus directe pour valoriser ton usage métier de Copilot.
+Quand : Après une pratique régulière de Microsoft 365 Copilot</t>
+  </si>
+  <si>
+    <t>Construire un socle commun sur les charges de travail IA et les services Azure AI.
+Compétences : Machine learning ; vision ; NLP ; IA générative ; principes d’IA responsable</t>
+  </si>
+  <si>
+    <t>⭐⭐⭐⭐⭐ Excellent socle conceptuel, reconnu et transversal.
+Quand : Au début du parcours ou en parallèle d’AB-730</t>
+  </si>
+  <si>
+    <t>Comprendre Power Platform pour automatiser, analyser et créer des solutions low-code.
+Compétences : Power Apps ; Power Automate ; Dataverse ; Power BI ; valeur métier de Power Platform</t>
+  </si>
+  <si>
+    <t>⭐⭐⭐⭐⭐ Complément naturel à Copilot Studio et aux agents.
+Quand : Après le socle IA, avant un parcours builder</t>
+  </si>
+  <si>
+    <t>Concevoir, intégrer, sécuriser, tester et exploiter des agents d’entreprise dans Copilot Studio.
+Compétences : Agent flows ; Dataverse ; connecteurs/API ; RAG ; MCP/A2A ; multi-agent ; ALM et gouvernance</t>
+  </si>
+  <si>
+    <t>⭐⭐⭐⭐ Très pertinent si tu veux construire et intégrer des agents.
+Quand : Après PL-900 et une pratique concrète de Copilot Studio</t>
+  </si>
+  <si>
+    <t>Acquérir le vocabulaire et les principes des données relationnelles, non relationnelles et analytiques.
+Compétences : Données relationnelles ; NoSQL ; analytics ; services de données Azure</t>
+  </si>
+  <si>
+    <t>⭐⭐⭐⭐ Bon bonus pour mieux comprendre les sources et architectures de données.
+Quand : Quand les sujets data, RAG ou gouvernance deviennent plus présents</t>
+  </si>
+  <si>
+    <t>Identifier la valeur de l’IA, choisir les solutions et piloter adoption, gouvernance et transformation.
+Compétences : Business value ; portefeuille Microsoft AI ; ROI ; IA responsable ; stratégie d’adoption et conduite du changement</t>
+  </si>
+  <si>
+    <t>⭐⭐⭐ Moins prioritaire aujourd’hui, mais très utile pour un rôle de management ou de sponsor.
+Quand : À remonter dans le classement si tu pilotes une adoption ou une transformation IA</t>
+  </si>
+  <si>
+    <t>Lien officiel</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/fr-fr/credentials/certifications/ai-business-professional/</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/fr-fr/credentials/certifications/azure-ai-fundamentals/</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/fr-fr/credentials/certifications/power-platform-fundamentals/</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/fr-fr/credentials/certifications/ai-agent-builder-associate/</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/fr-fr/credentials/certifications/azure-data-fundamentals/</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/fr-fr/credentials/certifications/ai-transformation-leader/</t>
+  </si>
+  <si>
+    <t>76 € HT*
+Examen payant ; préparation Microsoft Learn gratuite</t>
+  </si>
+  <si>
+    <t>165 USD* — prix France à confirmer lors de l’inscription
+Examen payant ; préparation Microsoft Learn gratuite</t>
+  </si>
+  <si>
+    <t>Prix de l’examen</t>
+  </si>
+  <si>
+    <t>PL-900
+Power Platform Fundamentals</t>
+  </si>
+  <si>
+    <t>AB-620
+AI Agent Builder Associate</t>
+  </si>
+  <si>
+    <t>DP-900
+Azure Data Fundamentals</t>
+  </si>
+  <si>
+    <t>AB-731
+AI Transformation Leader</t>
+  </si>
+  <si>
+    <t>Titre</t>
+  </si>
+  <si>
+    <t>AB-730
+AI Business Professional</t>
+  </si>
+  <si>
+    <t>AI-900
+Azure AI Fundamentals</t>
+  </si>
+  <si>
+    <t>Applied Skill
+Créer un agent dans Microsoft Copilot Studio</t>
+  </si>
+  <si>
+    <t>Applied Skills / Copilot Studio</t>
+  </si>
+  <si>
+    <t>Créateurs d’applications, utilisateurs métier, makers Copilot Studio</t>
+  </si>
+  <si>
+    <t>Démontrer la capacité à créer et publier un agent dans Copilot Studio.
+Compétences : configuration de l’agent ; IA générative et connaissances ; rubriques ; outils ; partage et publication.</t>
+  </si>
+  <si>
+    <t>⭐⭐⭐⭐⭐ Validation pratique directement utile avant un parcours builder avancé.
+Quand : après PL-900 et une première pratique de Copilot Studio. Préparation : 3 h 52 ; évaluation pratique : 2 h, en anglais.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/fr-fr/credentials/applied-skills/build-an-agent-in-microsoft-copilot-studio/</t>
+  </si>
+  <si>
+    <t>Gratuite*
+Parcours et évaluation Microsoft Learn</t>
+  </si>
+  <si>
+    <t>Applied Skill
+Améliorer les agents avec des fonctionnalités autonomes</t>
+  </si>
+  <si>
+    <t>Applied Skills / Agentique</t>
+  </si>
+  <si>
+    <t>Makers et développeurs connaissant Copilot Studio, Power Automate et Dataverse</t>
+  </si>
+  <si>
+    <t>Ajouter des capacités autonomes à un agent Copilot Studio.
+Compétences : connaissances ; agent flows comme outils ; déclencheurs d’événements ; gestion des erreurs ; interaction humaine.</t>
+  </si>
+  <si>
+    <t>⭐⭐⭐⭐⭐ Étape pratique idéale entre la création d’un agent simple et AB-620.
+Quand : après l’Applied Skill de création d’agent. Préparation : 2 h ; évaluation pratique : 45 min, en anglais.</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/fr-fr/credentials/applied-skills/enhance-agents-with-autonomous-capabilities/</t>
+  </si>
+  <si>
+    <t>🎓 Parcours de certifications et Applied Skills Microsoft IA</t>
+  </si>
+  <si>
+    <t>Créer un agent dans Copilot Studio ; Améliorer les agents avec des fonctionnalités autonomes</t>
+  </si>
+  <si>
+    <t>* Les certifications complètes sont payantes. Les deux Applied Skills sont accessibles comme évaluations pratiques Microsoft Learn sans prix affiché sur leur page ; vérifiez les conditions au lancement. Les prix d’examen varient selon le pays, la TVA et les promotions.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1744,8 +2385,53 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF666666"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF666666"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1761,6 +2447,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1787,10 +2479,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1817,15 +2510,105 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
+  <dxfs count="58">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="9"/>
+      </font>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment vertical="center" wrapText="1"/>
     </dxf>
@@ -1936,22 +2719,7 @@
       <alignment vertical="top" wrapText="1"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1964,6 +2732,27 @@
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1983,64 +2772,97 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F2E694E0-AB34-4AED-A4B0-70F4A6C6FD9A}" name="Tableau1" displayName="Tableau1" ref="A1:B67" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
-  <autoFilter ref="A1:B67" xr:uid="{F2E694E0-AB34-4AED-A4B0-70F4A6C6FD9A}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B67">
-    <sortCondition ref="A2:A67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F2E694E0-AB34-4AED-A4B0-70F4A6C6FD9A}" name="Tableau1" displayName="Tableau1" ref="A1:C107" totalsRowShown="0" headerRowDxfId="50" dataDxfId="49">
+  <autoFilter ref="A1:C107" xr:uid="{F2E694E0-AB34-4AED-A4B0-70F4A6C6FD9A}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C107">
+    <sortCondition ref="A1:A107"/>
   </sortState>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7684F4F8-1690-40E7-8A05-01AFE0046C3F}" name="Terme" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{1E9A4EF6-F4B9-4A30-89F3-E1CBE358BC02}" name="Description" dataDxfId="35"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{7684F4F8-1690-40E7-8A05-01AFE0046C3F}" name="Terme" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{645CD0EB-C40A-4026-B888-B4DFF61D93B4}" name="Catégorie" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{1E9A4EF6-F4B9-4A30-89F3-E1CBE358BC02}" name="Description" dataDxfId="46"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{19A2F625-536D-4BB4-A715-44521A0BF713}" name="Tableau5" displayName="Tableau5" ref="A4:E28" totalsRowShown="0" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{19A2F625-536D-4BB4-A715-44521A0BF713}" name="Tableau5" displayName="Tableau5" ref="A4:E28" totalsRowShown="0" dataDxfId="45">
   <autoFilter ref="A4:E28" xr:uid="{19A2F625-536D-4BB4-A715-44521A0BF713}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E4DD7A07-8F59-478F-A205-1A9D73E02923}" name="Agent" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{192DB2A5-732E-4639-AF11-42BEE1E52660}" name="Outil" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{CC902B46-127A-47B5-97EB-2316787E39A1}" name="Description" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{67653B42-7A91-4FAE-A366-C67349B5C19E}" name="Cas d'usage / Prompts" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{84D4DADC-F2D1-4488-B730-C8BBD10C5C70}" name="Quand l'utiliser" dataDxfId="23"/>
+    <tableColumn id="1" xr3:uid="{E4DD7A07-8F59-478F-A205-1A9D73E02923}" name="Agent" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{192DB2A5-732E-4639-AF11-42BEE1E52660}" name="Outil" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{CC902B46-127A-47B5-97EB-2316787E39A1}" name="Description" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{67653B42-7A91-4FAE-A366-C67349B5C19E}" name="Cas d'usage / Prompts" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{84D4DADC-F2D1-4488-B730-C8BBD10C5C70}" name="Quand l'utiliser" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{9675F539-DE25-4925-B6C7-40FC54A40625}" name="TableauConsolide" displayName="TableauConsolide" ref="A1:U16" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{9675F539-DE25-4925-B6C7-40FC54A40625}" name="TableauConsolide" displayName="TableauConsolide" ref="A1:U16" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
   <autoFilter ref="A1:U16" xr:uid="{9675F539-DE25-4925-B6C7-40FC54A40625}"/>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{26096A9F-090B-4462-A11F-FF5695A5A87D}" name="Catégorie" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{31AB6292-E168-4D7E-9353-B8B2F0FE70EA}" name="Usage(s)" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{8AB366EE-1200-43E4-8AEB-5AA34E3B6094}" name="Microsoft" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{1AAE1813-5818-4C4B-BAF5-FC0AE5BA5DF6}" name="Anthropic" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{A317F7B5-6BB9-48F4-9502-2967DF8FF5F5}" name="OpenAI" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{5FA7940D-DE75-4AA8-A215-C7C0A8512A63}" name="Google" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{10950D0E-02D8-4F8F-8EA9-3871D9AA7F60}" name="Perplexity" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{C9A420A3-EF97-42C8-B14C-59862764B684}" name="Salesforce" dataDxfId="13"/>
-    <tableColumn id="9" xr3:uid="{74FB21AB-6285-4F52-B943-C6372FD7B93E}" name="ServiceNow" dataDxfId="12"/>
-    <tableColumn id="10" xr3:uid="{011C63F1-5AB4-42F2-BF2A-F2E775841EF5}" name="SAP" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{CBBA0A27-F029-4AD7-A618-A2B9D2341A8F}" name="Oracle" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{63F34C1C-AC62-4FC3-A9A9-22C63C12BA52}" name="Atlassian" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{7B7D332E-1E93-404B-AF1C-1B8CB78B5952}" name="Amazon" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{580466D5-BA05-4A63-B707-415A7BEF61C2}" name="IBM" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{88DF00A4-2660-47EE-9BC0-1D429335EDB0}" name="Meta" dataDxfId="6"/>
-    <tableColumn id="16" xr3:uid="{27261DA4-FB0B-46B2-9AFA-DC5F44BB5BC1}" name="Mistral AI" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{4C7AA2E4-EDAB-4C7A-B71C-8891070C417D}" name="Cohere" dataDxfId="4"/>
-    <tableColumn id="18" xr3:uid="{6C934164-909C-48D2-B375-BA3D5C990858}" name="Hugging Face" dataDxfId="3"/>
-    <tableColumn id="19" xr3:uid="{D229C10B-5FD8-4448-8DBD-70C7A7F1B2F7}" name="N8N" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{B820B4EF-E3AB-4214-9307-8C233036B027}" name="Make" dataDxfId="1"/>
-    <tableColumn id="21" xr3:uid="{FD82EFDC-B79A-49BC-8CAC-80EB51A84556}" name="Zapier" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{26096A9F-090B-4462-A11F-FF5695A5A87D}" name="Catégorie" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{31AB6292-E168-4D7E-9353-B8B2F0FE70EA}" name="Usage(s)" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{8AB366EE-1200-43E4-8AEB-5AA34E3B6094}" name="Microsoft" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{1AAE1813-5818-4C4B-BAF5-FC0AE5BA5DF6}" name="Anthropic" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{A317F7B5-6BB9-48F4-9502-2967DF8FF5F5}" name="OpenAI" dataDxfId="33"/>
+    <tableColumn id="6" xr3:uid="{5FA7940D-DE75-4AA8-A215-C7C0A8512A63}" name="Google" dataDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{10950D0E-02D8-4F8F-8EA9-3871D9AA7F60}" name="Perplexity" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{C9A420A3-EF97-42C8-B14C-59862764B684}" name="Salesforce" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{74FB21AB-6285-4F52-B943-C6372FD7B93E}" name="ServiceNow" dataDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{011C63F1-5AB4-42F2-BF2A-F2E775841EF5}" name="SAP" dataDxfId="28"/>
+    <tableColumn id="11" xr3:uid="{CBBA0A27-F029-4AD7-A618-A2B9D2341A8F}" name="Oracle" dataDxfId="27"/>
+    <tableColumn id="12" xr3:uid="{63F34C1C-AC62-4FC3-A9A9-22C63C12BA52}" name="Atlassian" dataDxfId="26"/>
+    <tableColumn id="13" xr3:uid="{7B7D332E-1E93-404B-AF1C-1B8CB78B5952}" name="Amazon" dataDxfId="25"/>
+    <tableColumn id="14" xr3:uid="{580466D5-BA05-4A63-B707-415A7BEF61C2}" name="IBM" dataDxfId="24"/>
+    <tableColumn id="15" xr3:uid="{88DF00A4-2660-47EE-9BC0-1D429335EDB0}" name="Meta" dataDxfId="23"/>
+    <tableColumn id="16" xr3:uid="{27261DA4-FB0B-46B2-9AFA-DC5F44BB5BC1}" name="Mistral AI" dataDxfId="22"/>
+    <tableColumn id="17" xr3:uid="{4C7AA2E4-EDAB-4C7A-B71C-8891070C417D}" name="Cohere" dataDxfId="21"/>
+    <tableColumn id="18" xr3:uid="{6C934164-909C-48D2-B375-BA3D5C990858}" name="Hugging Face" dataDxfId="20"/>
+    <tableColumn id="19" xr3:uid="{D229C10B-5FD8-4448-8DBD-70C7A7F1B2F7}" name="N8N" dataDxfId="19"/>
+    <tableColumn id="20" xr3:uid="{B820B4EF-E3AB-4214-9307-8C233036B027}" name="Make" dataDxfId="18"/>
+    <tableColumn id="21" xr3:uid="{FD82EFDC-B79A-49BC-8CAC-80EB51A84556}" name="Zapier" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{ADDF4EEE-E50B-4023-B2AE-D75EC9BDFD6F}" name="Tableau8" displayName="Tableau8" ref="A15:D23" totalsRowShown="0" headerRowDxfId="57" dataDxfId="56">
+  <autoFilter ref="A15:D23" xr:uid="{ADDF4EEE-E50B-4023-B2AE-D75EC9BDFD6F}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{599D76A7-528D-4B9E-8F86-F147285E2A9D}" name="Repère" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{EAF6BF54-2906-4C94-AF9D-B8069A5DAE78}" name="Nature" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{7464192D-284F-456F-A935-318A4EB8029D}" name="Description" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{B0D65618-1B5E-4C5A-ACD8-2ABCDE27EBF2}" name="Exemples dans ce parcours" dataDxfId="52"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{47D179A4-938A-4E6C-B202-A0D78771812B}" name="Tableau7" displayName="Tableau7" ref="A4:J12" totalsRowShown="0" headerRowDxfId="51" dataDxfId="7">
+  <autoFilter ref="A4:J12" xr:uid="{47D179A4-938A-4E6C-B202-A0D78771812B}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{93188F5E-86D4-4B44-A7C0-7B7BF2457299}" name="Certification" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{203B31F0-7487-4CE7-95B9-9E2264A809D7}" name="Niveau" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{C14BEF3B-4D85-4A3B-A6E7-4E74EDCC41F5}" name="Titre" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{12127D4B-4C76-408D-9CED-BFE4B6A63B10}" name="Pour qui ?" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{362006E7-02C9-470C-9764-BD2ED0858D8E}" name="Objectif et compétences clés" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{E6CB48A6-5DC8-47B1-AF28-2E260915CC1D}" name="Priorité" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{D24D292E-DBC0-404F-941C-CFEBE4335D3B}" name="Ordre" dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{CB9CF23A-9387-40D9-91CC-DB42280CFC22}" name="Intérêt / moment conseillé" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{A9CD7D5E-8DF0-4455-844D-7A2BD967E6EA}" name="Lien officiel" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{BC67CCC5-7731-4053-AF63-CCC525FB3931}" name="Prix de l’examen" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{F814AA58-74C3-469A-A0FE-2FE33F6B87DC}" name="Tableau6" displayName="Tableau6" ref="A1:D5" totalsRowShown="0">
   <autoFilter ref="A1:D5" xr:uid="{F814AA58-74C3-469A-A0FE-2FE33F6B87DC}"/>
   <tableColumns count="4">
@@ -2053,7 +2875,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E53B3046-5CF2-4E52-BD8B-71AFEA478444}" name="Tableau2" displayName="Tableau2" ref="A8:C13" totalsRowShown="0">
   <autoFilter ref="A8:C13" xr:uid="{E53B3046-5CF2-4E52-BD8B-71AFEA478444}"/>
   <tableColumns count="3">
@@ -2065,23 +2887,23 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3FC98716-2DB0-44B0-B54C-3CD6EB5D71DD}" name="Tableau3" displayName="Tableau3" ref="B19:C35" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3FC98716-2DB0-44B0-B54C-3CD6EB5D71DD}" name="Tableau3" displayName="Tableau3" ref="B19:C35" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15">
   <autoFilter ref="B19:C35" xr:uid="{3FC98716-2DB0-44B0-B54C-3CD6EB5D71DD}"/>
   <tableColumns count="2">
-    <tableColumn id="2" xr3:uid="{B6820086-B98C-477B-8831-E7314ECD6971}" name="Usages" dataDxfId="32"/>
-    <tableColumn id="1" xr3:uid="{8223333B-20A1-43F7-9DC7-AA1B7638CF76}" name="Exemples de prompts complémentaires" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{B6820086-B98C-477B-8831-E7314ECD6971}" name="Usages" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{8223333B-20A1-43F7-9DC7-AA1B7638CF76}" name="Exemples de prompts complémentaires" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{26474631-F01B-4B0F-B67F-0DA61B1C2544}" name="Tableau4" displayName="Tableau4" ref="B1:C6" totalsRowShown="0">
   <autoFilter ref="B1:C6" xr:uid="{26474631-F01B-4B0F-B67F-0DA61B1C2544}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5D9EF20F-8F3A-459E-AA79-CB05307CE27F}" name="Stratégie" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{AC2369DE-430C-46EF-91C1-12A4275B5E58}" name="Exemple" dataDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{5D9EF20F-8F3A-459E-AA79-CB05307CE27F}" name="Stratégie" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{AC2369DE-430C-46EF-91C1-12A4275B5E58}" name="Exemple" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2407,547 +3229,1188 @@
   <sheetPr>
     <tabColor theme="9"/>
   </sheetPr>
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:C107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.08984375" customWidth="1"/>
-    <col min="2" max="2" width="102.90625" customWidth="1"/>
+    <col min="1" max="2" width="29.08984375" customWidth="1"/>
+    <col min="3" max="3" width="102.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="116" x14ac:dyDescent="0.35">
+      <c r="A6" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B6" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+    <row r="7" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A7" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A8" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A16" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A21" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A24" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A25" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A26" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A27" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A28" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A29" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A30" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A31" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A32" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A34" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A35" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A36" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A38" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A39" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A40" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A41" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A42" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A43" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A44" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A45" s="8" t="s">
+        <v>530</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="377" x14ac:dyDescent="0.35">
+      <c r="A46" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A48" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A50" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="87" x14ac:dyDescent="0.35">
+      <c r="A51" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A53" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A55" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A56" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="116" x14ac:dyDescent="0.35">
+      <c r="A57" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A58" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="145" x14ac:dyDescent="0.35">
+      <c r="A59" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A60" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A61" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A62" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A65" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A66" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A67" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="116" x14ac:dyDescent="0.35">
+      <c r="A69" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A70" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A71" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A72" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A73" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A74" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A75" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A76" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A77" s="8" t="s">
+        <v>532</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A78" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A80" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A81" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A82" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A83" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A84" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B84" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="C84" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="8" t="s">
+    <row r="85" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A85" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A86" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A87" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A88" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A89" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A90" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A91" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A92" s="8" t="s">
+        <v>575</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A93" s="8" t="s">
+        <v>566</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A94" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A95" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="116" x14ac:dyDescent="0.35">
+      <c r="A96" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A97" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A98" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="A99" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A101" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A102" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B102" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="C102" s="8" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="116" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7" s="8" t="s">
-        <v>472</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A8" s="8" t="s">
+    <row r="103" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A103" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="C103" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" s="8" t="s">
-        <v>447</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A14" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A17" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A19" s="8" t="s">
-        <v>459</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A20" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A22" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A23" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A24" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="8" t="s">
+    </row>
+    <row r="104" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A104" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B105" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="C105" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
-        <v>455</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A27" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A28" s="8" t="s">
+    <row r="106" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A106" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A107" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="C107" s="8" t="s">
         <v>418</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A29" s="8" t="s">
-        <v>416</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A30" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A32" s="8" t="s">
-        <v>470</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="87" x14ac:dyDescent="0.35">
-      <c r="A34" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A35" s="8" t="s">
-        <v>432</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A37" s="8" t="s">
-        <v>462</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="116" x14ac:dyDescent="0.35">
-      <c r="A38" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A41" s="8" t="s">
-        <v>474</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A43" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A44" s="8" t="s">
-        <v>451</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A45" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A46" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A47" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A48" s="8" t="s">
-        <v>457</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A50" s="8" t="s">
-        <v>449</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" ht="217.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A53" s="8" t="s">
-        <v>453</v>
-      </c>
-      <c r="B53" s="8" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B54" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A55" s="8" t="s">
-        <v>424</v>
-      </c>
-      <c r="B55" s="8" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A56" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A57" s="8" t="s">
-        <v>430</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A58" s="8" t="s">
-        <v>414</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A59" s="8" t="s">
-        <v>466</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A60" s="8" t="s">
-        <v>428</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" ht="58" x14ac:dyDescent="0.35">
-      <c r="A61" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B61" s="8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A63" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A64" s="8" t="s">
-        <v>436</v>
-      </c>
-      <c r="B64" s="8" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A65" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B65" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A66" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A67" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -2975,442 +4438,442 @@
   <sheetData>
     <row r="1" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="9" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
+      <c r="A2" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E4" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>113</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>327</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>114</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="8" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>331</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>332</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="8" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B8" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>335</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B10" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>342</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B12" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>349</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>353</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>372</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>373</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>374</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B20" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>376</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>377</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="8" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B22" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>383</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>384</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>385</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="8" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B23" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>387</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>389</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="8" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B24" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="E24" s="8" t="s">
         <v>391</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>392</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B25" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="E25" s="8" t="s">
         <v>395</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>396</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="8" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B27" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="E27" s="8" t="s">
         <v>402</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="80" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="8" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B28" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="E28" s="8" t="s">
         <v>406</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>407</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>409</v>
       </c>
     </row>
   </sheetData>
@@ -3440,1042 +4903,1042 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="O1" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="R1" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="P1" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q1" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="R1" s="6" t="s">
-        <v>221</v>
-      </c>
       <c r="S1" s="6" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="T1" s="6" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="U1" s="6" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="O2" s="7" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="Q2" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="R2" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="R2" s="7" t="s">
-        <v>233</v>
-      </c>
       <c r="S2" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="T2" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="U2" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>139</v>
-      </c>
       <c r="I3" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N3" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="O3" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P3" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Q3" s="7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="R3" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S3" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="T3" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="U3" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F4" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="M4" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>152</v>
-      </c>
       <c r="N4" s="7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="O4" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R4" s="7" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="S4" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="T4" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="U4" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F5" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="M5" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>152</v>
-      </c>
       <c r="N5" s="7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P5" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R5" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S5" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="T5" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="U5" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>217</v>
-      </c>
       <c r="F6" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="M6" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>152</v>
-      </c>
       <c r="N6" s="7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Q6" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="R6" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="R6" s="7" t="s">
-        <v>235</v>
-      </c>
       <c r="S6" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="T6" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="J7" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H7" s="7" t="s">
+      <c r="K7" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="L7" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="M7" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="N7" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="L7" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>177</v>
-      </c>
       <c r="O7" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P7" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S7" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="T7" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="U7" s="7" t="s">
         <v>297</v>
-      </c>
-      <c r="T7" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="U7" s="7" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="I8" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="F8" s="7" t="s">
+      <c r="J8" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H8" s="7" t="s">
+      <c r="K8" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="L8" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="M8" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="N8" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>186</v>
-      </c>
       <c r="O8" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S8" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="T8" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="U8" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="I9" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="F9" s="7" t="s">
+      <c r="K9" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H9" s="7" t="s">
+      <c r="L9" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="I9" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="J9" s="7" t="s">
+      <c r="M9" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="N9" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="L9" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>195</v>
-      </c>
       <c r="O9" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R9" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="S9" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="I10" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="F10" s="7" t="s">
+      <c r="K10" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="L10" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H10" s="7" t="s">
+      <c r="M10" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="I10" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>202</v>
-      </c>
       <c r="N10" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="P10" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R10" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S10" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="T10" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="U10" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="E11" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="G11" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="M11" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="N11" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>211</v>
-      </c>
       <c r="O11" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R11" s="7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="S11" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="E12" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="F12" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="G12" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="H12" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="I12" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="J12" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="K12" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="L12" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="M12" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="N12" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="O12" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q12" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="M12" s="7" t="s">
+      <c r="R12" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="N12" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="P12" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q12" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="R12" s="7" t="s">
-        <v>253</v>
-      </c>
       <c r="S12" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="T12" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="U12" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="E13" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="F13" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="G13" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="I13" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="J13" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H13" s="7" t="s">
+      <c r="K13" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="L13" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="M13" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="N13" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="K13" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>265</v>
-      </c>
       <c r="O13" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="T13" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="U13" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="E14" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="F14" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="G14" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="I14" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="K14" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="L14" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H14" s="7" t="s">
+      <c r="M14" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="I14" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="J14" s="7" t="s">
+      <c r="N14" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="K14" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="L14" s="7" t="s">
+      <c r="O14" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="M14" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>277</v>
-      </c>
       <c r="P14" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="T14" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="U14" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="F15" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="G15" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="M15" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E15" s="7" t="s">
+      <c r="N15" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="R15" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="O15" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="P15" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q15" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="R15" s="7" t="s">
-        <v>284</v>
-      </c>
       <c r="S15" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="U15" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="F16" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="G16" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E16" s="7" t="s">
+      <c r="I16" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="M16" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="N16" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="H16" s="7" t="s">
+      <c r="O16" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="R16" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="I16" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="N16" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="O16" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="P16" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q16" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="R16" s="7" t="s">
-        <v>293</v>
-      </c>
       <c r="S16" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="T16" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="U16" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -4487,6 +5950,515 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73B6B774-C85E-4077-897D-BFFAF66F7C99}">
+  <sheetPr>
+    <tabColor theme="9"/>
+  </sheetPr>
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="23.6328125" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7265625" customWidth="1"/>
+    <col min="4" max="4" width="15.453125" customWidth="1"/>
+    <col min="5" max="5" width="23.6328125" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="7.26953125" customWidth="1"/>
+    <col min="8" max="8" width="19.08984375" customWidth="1"/>
+    <col min="9" max="9" width="20.90625" customWidth="1"/>
+    <col min="10" max="10" width="15.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="15" t="s">
+        <v>680</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+    </row>
+    <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="16" t="s">
+        <v>592</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>583</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>584</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>664</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>635</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>637</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
+        <v>665</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>586</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>597</v>
+      </c>
+      <c r="G5" s="12">
+        <v>1</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>651</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="116" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
+        <v>666</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>640</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>600</v>
+      </c>
+      <c r="G6" s="12">
+        <v>2</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>652</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="130.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
+        <v>660</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>601</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>600</v>
+      </c>
+      <c r="G7" s="12">
+        <v>3</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>653</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="174" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>667</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>603</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>668</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>600</v>
+      </c>
+      <c r="G8" s="12">
+        <v>4</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>672</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
+        <v>674</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>603</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>600</v>
+      </c>
+      <c r="G9" s="12">
+        <v>5</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>679</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="145" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>661</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>603</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>604</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>605</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>644</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>606</v>
+      </c>
+      <c r="G10" s="12">
+        <v>6</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>654</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>662</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>607</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="G11" s="12">
+        <v>7</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>655</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="11" t="s">
+        <v>663</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>612</v>
+      </c>
+      <c r="G12" s="12">
+        <v>8</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>656</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13" s="18" t="s">
+        <v>682</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14" s="17" t="s">
+        <v>613</v>
+      </c>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>615</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="A16" s="10" t="s">
+        <v>595</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="10" t="s">
+        <v>603</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A18" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A19" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A20" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="10" t="s">
+        <v>591</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="87" x14ac:dyDescent="0.35">
+      <c r="A22" s="10" t="s">
+        <v>587</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>681</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A13:J13"/>
+  </mergeCells>
+  <phoneticPr fontId="9" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I5" r:id="rId1" xr:uid="{9E3B7034-794D-4CF3-87C3-B357D9B3EBBF}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{100B1F53-9825-43F2-BE04-88450A0E3B1E}">
   <sheetPr>
     <tabColor theme="9"/>
@@ -4502,72 +6474,72 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="D1" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B2" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C2" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="D2" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B3" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C3" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D3" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B4" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C4" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B5" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C5" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="D5" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -4578,7 +6550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAD6F939-8E80-4350-BCB2-0C615A686F58}">
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
@@ -4593,236 +6565,236 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="174" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B4" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="B5" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" t="s">
         <v>67</v>
-      </c>
-      <c r="C12" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B19" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B21" s="1"/>
       <c r="C21" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B22" s="1"/>
       <c r="C22" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="29" x14ac:dyDescent="0.35">
       <c r="B23" s="1"/>
       <c r="C23" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="29" x14ac:dyDescent="0.35">
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="58" x14ac:dyDescent="0.35">
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="29" x14ac:dyDescent="0.35">
       <c r="B28" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="29" x14ac:dyDescent="0.35">
       <c r="B29" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B30" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="2:3" ht="29" x14ac:dyDescent="0.35">
       <c r="B31" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="29" x14ac:dyDescent="0.35">
       <c r="B32" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="29" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="29" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="2:3" ht="29" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
